--- a/src/分类sku/demo.xlsx
+++ b/src/分类sku/demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\py\sci\src\分类sku\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24486F0-7242-4762-8BD5-726B8E0AD8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50074371-F777-4267-B1ED-DAD595980679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3990" yWindow="6435" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="demo" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,6 @@
     <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
     <sheet name="meta" sheetId="3" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">demo!$A$1:$D$4547</definedName>
   </definedNames>
@@ -43,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19638" uniqueCount="6029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19691" uniqueCount="6031">
   <si>
     <t>name</t>
   </si>
@@ -18132,6 +18129,13 @@
   </si>
   <si>
     <t>华</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>充电头,数据线</t>
+  </si>
+  <si>
+    <t>数据线</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -18192,628 +18196,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>商品简称</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>series</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>type</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="B2" t="str">
-            <v>VO200W线【C-C】线【1.5米2根，2米2根】</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>vo</v>
-          </cell>
-          <cell r="D2" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>足功率 【100W闪充头+2米线】</v>
-          </cell>
-          <cell r="C3" t="str">
-            <v>三星</v>
-          </cell>
-          <cell r="D3" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>三星 【45W快充头+1米线+2米线】</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>三星</v>
-          </cell>
-          <cell r="D4" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>三星 【45W快充头+1.5米线】</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>三星</v>
-          </cell>
-          <cell r="D5" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>一加 【80W闪充头单头】</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D6" t="str">
-            <v>充电头</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>华66双口头 【66W快充头+1.5米线+2米线】</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>华</v>
-          </cell>
-          <cell r="D7" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>一加 【80W闪充头+2米线】</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D8" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>一加 【80W闪充头+1米线】</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D9" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>足功率 【120W闪充头+1米线】</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>三星</v>
-          </cell>
-          <cell r="D10" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>一加 【100W闪充头+1米线+1.5米线】</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D11" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>OPPO 【67W闪充头+1米线】</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D12" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>华max原ic头G 【100W快充头+1.5米线】</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>华</v>
-          </cell>
-          <cell r="D13" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>华66双口头 【66W快充头+2米线】</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>华</v>
-          </cell>
-          <cell r="D14" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>OPPO 【80W闪充头+2米线】</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D15" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>华6a线 6A线【1米线】</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>华</v>
-          </cell>
-          <cell r="D16" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>一加 【100W闪充头单头】</v>
-          </cell>
-          <cell r="C17" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D17" t="str">
-            <v>充电头</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>一加 【100W闪充头+2米线】</v>
-          </cell>
-          <cell r="C18" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D18" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>OPPO 10A闪充线【1.5米线】</v>
-          </cell>
-          <cell r="C19" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D19" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>OPPO 10A闪充线【2米线】</v>
-          </cell>
-          <cell r="C20" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D20" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>华max原ic头G 【100W快充头+1米线】</v>
-          </cell>
-          <cell r="C21" t="str">
-            <v>华</v>
-          </cell>
-          <cell r="D21" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>荣max 66W快充头+1米线+2米线</v>
-          </cell>
-          <cell r="C22" t="str">
-            <v>华</v>
-          </cell>
-          <cell r="D22" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>一加 【80W闪充头+1米线+1.5米线】</v>
-          </cell>
-          <cell r="C23" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D23" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>三星 【45W快充头单头】</v>
-          </cell>
-          <cell r="C24" t="str">
-            <v>三星</v>
-          </cell>
-          <cell r="D24" t="str">
-            <v>充电头</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>一加 【100W闪充头+1米线】</v>
-          </cell>
-          <cell r="C25" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D25" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>华66双口头 【66W快充头单头】</v>
-          </cell>
-          <cell r="C26" t="str">
-            <v>华</v>
-          </cell>
-          <cell r="D26" t="str">
-            <v>充电头</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>一加 【100W闪充头+1.5米线】</v>
-          </cell>
-          <cell r="C27" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D27" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>足功率 【100W闪充头+1.5米线】</v>
-          </cell>
-          <cell r="C28" t="str">
-            <v>三星</v>
-          </cell>
-          <cell r="D28" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="str">
-            <v>OPPO 【67W闪充头+1.5米线】</v>
-          </cell>
-          <cell r="C29" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D29" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>苹果30W+苹果15【C-C】编制线 【30W快充头+1米线】</v>
-          </cell>
-          <cell r="C30" t="str">
-            <v>苹果</v>
-          </cell>
-          <cell r="D30" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="str">
-            <v>一嘉红线【USB-C】一加闪充线【6/6T/5/5T/3/3T】【1.5</v>
-          </cell>
-          <cell r="C31" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D31" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>OPPO 【67W闪充头+2米线】</v>
-          </cell>
-          <cell r="C32" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D32" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>VO33W-80W线6A闪充线【1米线+1.5米线】</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v>vo</v>
-          </cell>
-          <cell r="D33" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>MI-120W金标头G【米14PRO单头】120W头</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>小米</v>
-          </cell>
-          <cell r="D34" t="str">
-            <v>充电头</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>华MAX原IC头G 【100W快充头+1米线+1.5米线】</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v>华</v>
-          </cell>
-          <cell r="D35" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="str">
-            <v>一加 【80W闪充头+1.5米线+2米线】</v>
-          </cell>
-          <cell r="C36" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D36" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37" t="str">
-            <v>爆款数据线三星双TPC线|1米线(两条)</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v>三星</v>
-          </cell>
-          <cell r="D37" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38" t="str">
-            <v>OPPO 【80W闪充头+1米线】</v>
-          </cell>
-          <cell r="C38" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D38" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39" t="str">
-            <v>爆款数据线笔记本双TPC线|1.5米线(两条)</v>
-          </cell>
-          <cell r="C39" t="str">
-            <v>笔记本</v>
-          </cell>
-          <cell r="D39" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40" t="str">
-            <v>OP240W线【C-C】【1米线+1.5米线+2米线】三条</v>
-          </cell>
-          <cell r="C40" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D40" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="B41" t="str">
-            <v>华66双口头【66W快充头+1米线+1.5米线】</v>
-          </cell>
-          <cell r="C41" t="str">
-            <v>华</v>
-          </cell>
-          <cell r="D41" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42" t="str">
-            <v>OPPO 10A闪充线【1米线】</v>
-          </cell>
-          <cell r="C42" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D42" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="B43" t="str">
-            <v>一加 【80W闪充头+1.5米线】</v>
-          </cell>
-          <cell r="C43" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D43" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="B44" t="str">
-            <v>MAX40W大壳头G【单头】40W超级闪充头</v>
-          </cell>
-          <cell r="C44" t="str">
-            <v>三星</v>
-          </cell>
-          <cell r="D44" t="str">
-            <v>充电头</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="B45" t="str">
-            <v>苹果30W+苹果15【C-C】编制线 【30W快充头+1米线+1.5米线】</v>
-          </cell>
-          <cell r="C45" t="str">
-            <v>苹果</v>
-          </cell>
-          <cell r="D45" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="B46" t="str">
-            <v>主推数据线OPPO闪充线|2米线(一条)</v>
-          </cell>
-          <cell r="C46" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D46" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="B47" t="str">
-            <v>OPPO 10A数据线【1.5米线】</v>
-          </cell>
-          <cell r="C47" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D47" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="B48" t="str">
-            <v>米6A线全兼容闪充数据线1.5米</v>
-          </cell>
-          <cell r="C48" t="str">
-            <v>小米</v>
-          </cell>
-          <cell r="D48" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="B49" t="str">
-            <v>OPPO【65W闪充头+2米线】</v>
-          </cell>
-          <cell r="C49" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D49" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="B50" t="str">
-            <v>苹果30W+苹果15【C-C】编制线 【30W快充头+2米线】</v>
-          </cell>
-          <cell r="C50" t="str">
-            <v>苹果</v>
-          </cell>
-          <cell r="D50" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="B51" t="str">
-            <v>主推数据线OPPO闪充线|2米线(两条)</v>
-          </cell>
-          <cell r="C51" t="str">
-            <v>op</v>
-          </cell>
-          <cell r="D51" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="B52" t="str">
-            <v>主推数据线苹果15编织线|2米线(一条)</v>
-          </cell>
-          <cell r="C52" t="str">
-            <v>苹果</v>
-          </cell>
-          <cell r="D52" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="B53" t="str">
-            <v>一嘉红线【USB-C】一加闪充线【6/6T/5/5T/3/3T】【2米】</v>
-          </cell>
-          <cell r="C53" t="str">
-            <v>一加</v>
-          </cell>
-          <cell r="D53" t="str">
-            <v>数据线</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="B54" t="str">
-            <v>华MAX原IC头G 【100W快充头+2米线】</v>
-          </cell>
-          <cell r="C54" t="str">
-            <v>华</v>
-          </cell>
-          <cell r="D54" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="B55" t="str">
-            <v>华MAX原IC头G 【100W快充头+1.5米线+2米线】</v>
-          </cell>
-          <cell r="C55" t="str">
-            <v>华</v>
-          </cell>
-          <cell r="D55" t="str">
-            <v>充电头,数据线</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -79257,8 +78639,8 @@
       <c r="C4298" t="s">
         <v>5962</v>
       </c>
-      <c r="D4298" t="e">
-        <v>#N/A</v>
+      <c r="D4298" t="s">
+        <v>6030</v>
       </c>
     </row>
     <row r="4299" spans="1:4" x14ac:dyDescent="0.2">
@@ -82390,13 +81772,11 @@
       <c r="B4522" t="s">
         <v>5845</v>
       </c>
-      <c r="C4522" t="str">
-        <f>VLOOKUP(A4522,[1]Sheet1!$B:$C,2,)</f>
-        <v>苹果</v>
-      </c>
-      <c r="D4522" t="str">
-        <f>VLOOKUP(A4522,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头,数据线</v>
+      <c r="C4522" t="s">
+        <v>5957</v>
+      </c>
+      <c r="D4522" t="s">
+        <v>6029</v>
       </c>
     </row>
     <row r="4523" spans="1:4" x14ac:dyDescent="0.2">
@@ -82406,13 +81786,11 @@
       <c r="B4523" t="s">
         <v>3438</v>
       </c>
-      <c r="C4523" t="str">
-        <f>VLOOKUP(A4523,[1]Sheet1!$B:$C,2,)</f>
-        <v>一加</v>
-      </c>
-      <c r="D4523" t="str">
-        <f>VLOOKUP(A4523,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4523" t="s">
+        <v>5953</v>
+      </c>
+      <c r="D4523" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4524" spans="1:4" x14ac:dyDescent="0.2">
@@ -82422,13 +81800,11 @@
       <c r="B4524" t="s">
         <v>3950</v>
       </c>
-      <c r="C4524" t="str">
-        <f>VLOOKUP(A4524,[1]Sheet1!$B:$C,2,)</f>
-        <v>op</v>
-      </c>
-      <c r="D4524" t="str">
-        <f>VLOOKUP(A4524,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头,数据线</v>
+      <c r="C4524" t="s">
+        <v>5960</v>
+      </c>
+      <c r="D4524" t="s">
+        <v>6029</v>
       </c>
     </row>
     <row r="4525" spans="1:4" x14ac:dyDescent="0.2">
@@ -82438,13 +81814,11 @@
       <c r="B4525" t="s">
         <v>5997</v>
       </c>
-      <c r="C4525" t="str">
-        <f>VLOOKUP(A4525,[1]Sheet1!$B:$C,2,)</f>
-        <v>vo</v>
-      </c>
-      <c r="D4525" t="str">
-        <f>VLOOKUP(A4525,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4525" t="s">
+        <v>5962</v>
+      </c>
+      <c r="D4525" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4526" spans="1:4" x14ac:dyDescent="0.2">
@@ -82454,13 +81828,11 @@
       <c r="B4526" t="s">
         <v>3490</v>
       </c>
-      <c r="C4526" t="str">
-        <f>VLOOKUP(A4526,[1]Sheet1!$B:$C,2,)</f>
-        <v>小米</v>
-      </c>
-      <c r="D4526" t="str">
-        <f>VLOOKUP(A4526,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头</v>
+      <c r="C4526" t="s">
+        <v>5955</v>
+      </c>
+      <c r="D4526" t="s">
+        <v>5951</v>
       </c>
     </row>
     <row r="4527" spans="1:4" x14ac:dyDescent="0.2">
@@ -82470,13 +81842,11 @@
       <c r="B4527" t="s">
         <v>5796</v>
       </c>
-      <c r="C4527" t="str">
-        <f>VLOOKUP(A4527,[1]Sheet1!$B:$C,2,)</f>
-        <v>华</v>
-      </c>
-      <c r="D4527" t="str">
-        <f>VLOOKUP(A4527,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头,数据线</v>
+      <c r="C4527" t="s">
+        <v>5961</v>
+      </c>
+      <c r="D4527" t="s">
+        <v>6029</v>
       </c>
     </row>
     <row r="4528" spans="1:4" x14ac:dyDescent="0.2">
@@ -82486,13 +81856,11 @@
       <c r="B4528" t="s">
         <v>6001</v>
       </c>
-      <c r="C4528" t="str">
-        <f>VLOOKUP(A4528,[1]Sheet1!$B:$C,2,)</f>
-        <v>一加</v>
-      </c>
-      <c r="D4528" t="str">
-        <f>VLOOKUP(A4528,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头,数据线</v>
+      <c r="C4528" t="s">
+        <v>5953</v>
+      </c>
+      <c r="D4528" t="s">
+        <v>6029</v>
       </c>
     </row>
     <row r="4529" spans="1:4" x14ac:dyDescent="0.2">
@@ -82502,13 +81870,11 @@
       <c r="B4529" t="s">
         <v>6003</v>
       </c>
-      <c r="C4529" t="str">
-        <f>VLOOKUP(A4529,[1]Sheet1!$B:$C,2,)</f>
-        <v>三星</v>
-      </c>
-      <c r="D4529" t="str">
-        <f>VLOOKUP(A4529,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4529" t="s">
+        <v>5952</v>
+      </c>
+      <c r="D4529" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4530" spans="1:4" x14ac:dyDescent="0.2">
@@ -82518,13 +81884,11 @@
       <c r="B4530" t="s">
         <v>3878</v>
       </c>
-      <c r="C4530" t="str">
-        <f>VLOOKUP(A4530,[1]Sheet1!$B:$C,2,)</f>
-        <v>op</v>
-      </c>
-      <c r="D4530" t="str">
-        <f>VLOOKUP(A4530,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头,数据线</v>
+      <c r="C4530" t="s">
+        <v>5960</v>
+      </c>
+      <c r="D4530" t="s">
+        <v>6029</v>
       </c>
     </row>
     <row r="4531" spans="1:4" x14ac:dyDescent="0.2">
@@ -82534,13 +81898,11 @@
       <c r="B4531" t="s">
         <v>6006</v>
       </c>
-      <c r="C4531" t="str">
-        <f>VLOOKUP(A4531,[1]Sheet1!$B:$C,2,)</f>
-        <v>笔记本</v>
-      </c>
-      <c r="D4531" t="str">
-        <f>VLOOKUP(A4531,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4531" t="s">
+        <v>5954</v>
+      </c>
+      <c r="D4531" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4532" spans="1:4" x14ac:dyDescent="0.2">
@@ -82550,13 +81912,11 @@
       <c r="B4532" t="s">
         <v>6008</v>
       </c>
-      <c r="C4532" t="str">
-        <f>VLOOKUP(A4532,[1]Sheet1!$B:$C,2,)</f>
-        <v>op</v>
-      </c>
-      <c r="D4532" t="str">
-        <f>VLOOKUP(A4532,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4532" t="s">
+        <v>5960</v>
+      </c>
+      <c r="D4532" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4533" spans="1:4" x14ac:dyDescent="0.2">
@@ -82566,13 +81926,11 @@
       <c r="B4533" t="s">
         <v>6010</v>
       </c>
-      <c r="C4533" t="str">
-        <f>VLOOKUP(A4533,[1]Sheet1!$B:$C,2,)</f>
-        <v>华</v>
-      </c>
-      <c r="D4533" t="str">
-        <f>VLOOKUP(A4533,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头,数据线</v>
+      <c r="C4533" t="s">
+        <v>5961</v>
+      </c>
+      <c r="D4533" t="s">
+        <v>6029</v>
       </c>
     </row>
     <row r="4534" spans="1:4" x14ac:dyDescent="0.2">
@@ -82582,13 +81940,11 @@
       <c r="B4534" t="s">
         <v>3429</v>
       </c>
-      <c r="C4534" t="str">
-        <f>VLOOKUP(A4534,[1]Sheet1!$B:$C,2,)</f>
-        <v>op</v>
-      </c>
-      <c r="D4534" t="str">
-        <f>VLOOKUP(A4534,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4534" t="s">
+        <v>5960</v>
+      </c>
+      <c r="D4534" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4535" spans="1:4" x14ac:dyDescent="0.2">
@@ -82598,13 +81954,11 @@
       <c r="B4535" t="s">
         <v>3465</v>
       </c>
-      <c r="C4535" t="str">
-        <f>VLOOKUP(A4535,[1]Sheet1!$B:$C,2,)</f>
-        <v>一加</v>
-      </c>
-      <c r="D4535" t="str">
-        <f>VLOOKUP(A4535,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头,数据线</v>
+      <c r="C4535" t="s">
+        <v>5953</v>
+      </c>
+      <c r="D4535" t="s">
+        <v>6029</v>
       </c>
     </row>
     <row r="4536" spans="1:4" x14ac:dyDescent="0.2">
@@ -82614,13 +81968,11 @@
       <c r="B4536" t="s">
         <v>3660</v>
       </c>
-      <c r="C4536" t="str">
-        <f>VLOOKUP(A4536,[1]Sheet1!$B:$C,2,)</f>
-        <v>三星</v>
-      </c>
-      <c r="D4536" t="str">
-        <f>VLOOKUP(A4536,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头</v>
+      <c r="C4536" t="s">
+        <v>5952</v>
+      </c>
+      <c r="D4536" t="s">
+        <v>5951</v>
       </c>
     </row>
     <row r="4537" spans="1:4" x14ac:dyDescent="0.2">
@@ -82630,13 +81982,11 @@
       <c r="B4537" t="s">
         <v>6015</v>
       </c>
-      <c r="C4537" t="str">
-        <f>VLOOKUP(A4537,[1]Sheet1!$B:$C,2,)</f>
-        <v>苹果</v>
-      </c>
-      <c r="D4537" t="str">
-        <f>VLOOKUP(A4537,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4537" t="s">
+        <v>5957</v>
+      </c>
+      <c r="D4537" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4538" spans="1:4" x14ac:dyDescent="0.2">
@@ -82646,13 +81996,11 @@
       <c r="B4538" t="s">
         <v>3804</v>
       </c>
-      <c r="C4538" t="str">
-        <f>VLOOKUP(A4538,[1]Sheet1!$B:$C,2,)</f>
-        <v>op</v>
-      </c>
-      <c r="D4538" t="str">
-        <f>VLOOKUP(A4538,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4538" t="s">
+        <v>5960</v>
+      </c>
+      <c r="D4538" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4539" spans="1:4" x14ac:dyDescent="0.2">
@@ -82662,13 +82010,11 @@
       <c r="B4539" t="s">
         <v>3431</v>
       </c>
-      <c r="C4539" t="str">
-        <f>VLOOKUP(A4539,[1]Sheet1!$B:$C,2,)</f>
-        <v>op</v>
-      </c>
-      <c r="D4539" t="str">
-        <f>VLOOKUP(A4539,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4539" t="s">
+        <v>5960</v>
+      </c>
+      <c r="D4539" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4540" spans="1:4" x14ac:dyDescent="0.2">
@@ -82678,13 +82024,11 @@
       <c r="B4540" t="s">
         <v>3483</v>
       </c>
-      <c r="C4540" t="str">
-        <f>VLOOKUP(A4540,[1]Sheet1!$B:$C,2,)</f>
-        <v>小米</v>
-      </c>
-      <c r="D4540" t="str">
-        <f>VLOOKUP(A4540,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4540" t="s">
+        <v>5955</v>
+      </c>
+      <c r="D4540" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4541" spans="1:4" x14ac:dyDescent="0.2">
@@ -82694,13 +82038,11 @@
       <c r="B4541" t="s">
         <v>4044</v>
       </c>
-      <c r="C4541" t="str">
-        <f>VLOOKUP(A4541,[1]Sheet1!$B:$C,2,)</f>
-        <v>op</v>
-      </c>
-      <c r="D4541" t="str">
-        <f>VLOOKUP(A4541,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头,数据线</v>
+      <c r="C4541" t="s">
+        <v>5960</v>
+      </c>
+      <c r="D4541" t="s">
+        <v>6029</v>
       </c>
     </row>
     <row r="4542" spans="1:4" x14ac:dyDescent="0.2">
@@ -82710,13 +82052,11 @@
       <c r="B4542" t="s">
         <v>6021</v>
       </c>
-      <c r="C4542" t="str">
-        <f>VLOOKUP(A4542,[1]Sheet1!$B:$C,2,)</f>
-        <v>苹果</v>
-      </c>
-      <c r="D4542" t="str">
-        <f>VLOOKUP(A4542,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头,数据线</v>
+      <c r="C4542" t="s">
+        <v>5957</v>
+      </c>
+      <c r="D4542" t="s">
+        <v>6029</v>
       </c>
     </row>
     <row r="4543" spans="1:4" x14ac:dyDescent="0.2">
@@ -82726,13 +82066,11 @@
       <c r="B4543" t="s">
         <v>4024</v>
       </c>
-      <c r="C4543" t="str">
-        <f>VLOOKUP(A4543,[1]Sheet1!$B:$C,2,)</f>
-        <v>op</v>
-      </c>
-      <c r="D4543" t="str">
-        <f>VLOOKUP(A4543,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4543" t="s">
+        <v>5960</v>
+      </c>
+      <c r="D4543" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4544" spans="1:4" x14ac:dyDescent="0.2">
@@ -82742,13 +82080,11 @@
       <c r="B4544" t="s">
         <v>3605</v>
       </c>
-      <c r="C4544" t="str">
-        <f>VLOOKUP(A4544,[1]Sheet1!$B:$C,2,)</f>
-        <v>苹果</v>
-      </c>
-      <c r="D4544" t="str">
-        <f>VLOOKUP(A4544,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4544" t="s">
+        <v>5957</v>
+      </c>
+      <c r="D4544" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4545" spans="1:4" x14ac:dyDescent="0.2">
@@ -82758,13 +82094,11 @@
       <c r="B4545" t="s">
         <v>3436</v>
       </c>
-      <c r="C4545" t="str">
-        <f>VLOOKUP(A4545,[1]Sheet1!$B:$C,2,)</f>
-        <v>一加</v>
-      </c>
-      <c r="D4545" t="str">
-        <f>VLOOKUP(A4545,[1]Sheet1!$B:$D,3,)</f>
-        <v>数据线</v>
+      <c r="C4545" t="s">
+        <v>5953</v>
+      </c>
+      <c r="D4545" t="s">
+        <v>3118</v>
       </c>
     </row>
     <row r="4546" spans="1:4" x14ac:dyDescent="0.2">
@@ -82774,13 +82108,11 @@
       <c r="B4546" t="s">
         <v>3653</v>
       </c>
-      <c r="C4546" t="str">
-        <f>VLOOKUP(A4546,[1]Sheet1!$B:$C,2,)</f>
-        <v>华</v>
-      </c>
-      <c r="D4546" t="str">
-        <f>VLOOKUP(A4546,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头,数据线</v>
+      <c r="C4546" t="s">
+        <v>5961</v>
+      </c>
+      <c r="D4546" t="s">
+        <v>6029</v>
       </c>
     </row>
     <row r="4547" spans="1:4" x14ac:dyDescent="0.2">
@@ -82790,13 +82122,11 @@
       <c r="B4547" t="s">
         <v>3669</v>
       </c>
-      <c r="C4547" t="str">
-        <f>VLOOKUP(A4547,[1]Sheet1!$B:$C,2,)</f>
-        <v>华</v>
-      </c>
-      <c r="D4547" t="str">
-        <f>VLOOKUP(A4547,[1]Sheet1!$B:$D,3,)</f>
-        <v>充电头,数据线</v>
+      <c r="C4547" t="s">
+        <v>5961</v>
+      </c>
+      <c r="D4547" t="s">
+        <v>6029</v>
       </c>
     </row>
   </sheetData>

--- a/src/分类sku/demo.xlsx
+++ b/src/分类sku/demo.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\py\sci\src\分类sku\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50074371-F777-4267-B1ED-DAD595980679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC80FD61-47EF-4902-BEF9-26AD181DC6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3990" yWindow="6435" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="demo" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
     <sheet name="meta" sheetId="3" r:id="rId4"/>
+    <sheet name="test" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">demo!$A$1:$D$4547</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19691" uniqueCount="6031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20003" uniqueCount="6235">
   <si>
     <t>name</t>
   </si>
@@ -18137,6 +18138,618 @@
   <si>
     <t>数据线</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平板12w【iPad套装】快充头+2米数据线</t>
+  </si>
+  <si>
+    <t>苹果30W+苹果15【C-C】编制线 【30W快充头+1.5米线+2米线】</t>
+  </si>
+  <si>
+    <t>平果15编织线【C-C】-1.5米,平果15编织线【C-C】-2米,苹果PD30w头-30w</t>
+  </si>
+  <si>
+    <t>华max原ic头G 【100W快充头单头】</t>
+  </si>
+  <si>
+    <t>华max原ic头G 【100W快充头+1.5米线+2米线】</t>
+  </si>
+  <si>
+    <t>华max原ic头G 【100W快充头+2米线】</t>
+  </si>
+  <si>
+    <t>苹果30W+苹果15【C-C】编制线 【30W快充头+1米线+2米线】</t>
+  </si>
+  <si>
+    <t>平果15编织线【C-C】-1米,平果15编织线【C-C】-2米,苹果PD30w头-30w</t>
+  </si>
+  <si>
+    <t>平板12w【iPad套装】快充头+1米数据线</t>
+  </si>
+  <si>
+    <t>华6a线 6A线【1米线+1.5米线】</t>
+  </si>
+  <si>
+    <t>主推数据线努比亚双tpc快充线|1米线(一条)</t>
+  </si>
+  <si>
+    <t>华6a线【C-C】【双TYPE-C口】闪充线2米</t>
+  </si>
+  <si>
+    <t>爆款数据线oppo闪充线|1米线(两条)</t>
+  </si>
+  <si>
+    <t>平果15编织线【C-C】【2米】iPad11快充编织线</t>
+  </si>
+  <si>
+    <t>爆款数据线安卓梯形micro线|1.5米线(两条)</t>
+  </si>
+  <si>
+    <t>OPPO线闪充1.5米线 +2米线</t>
+  </si>
+  <si>
+    <t>苹果30W+苹果15【C-C】编制线 【30W快充头+1.5米线】</t>
+  </si>
+  <si>
+    <t>OPPO 闪充线【1米线】</t>
+  </si>
+  <si>
+    <t>华66双口头 【66W快充头+1.5米线】</t>
+  </si>
+  <si>
+    <t>OPPO 【80W闪充头+1.5米线】</t>
+  </si>
+  <si>
+    <t>苹果30W+【C-C】编制线【套装】30W快充头+2米线</t>
+  </si>
+  <si>
+    <t>华6a线 6A线【2米线】</t>
+  </si>
+  <si>
+    <t>华max原ic头G 【100W快充头+1米线+2米线】</t>
+  </si>
+  <si>
+    <t>爆款数据线vivo快充线|1米线(一条)</t>
+  </si>
+  <si>
+    <t>苹果PD线30W快充线【1米+1.5米线】</t>
+  </si>
+  <si>
+    <t>平果PD线-1.5米,平果PD线-1米</t>
+  </si>
+  <si>
+    <t>华6a线【C-C】【双TYPE-C口】闪充线1.5米</t>
+  </si>
+  <si>
+    <t>VO【80W闪充头+2米线】</t>
+  </si>
+  <si>
+    <t>max40w大壳头G【单头】40W闪充头</t>
+  </si>
+  <si>
+    <t>主推数据线oppo闪充线|1.5米线(两条)</t>
+  </si>
+  <si>
+    <t>华66双口头 【66W快充头+1米线】</t>
+  </si>
+  <si>
+    <t>苹果30WPD头【单头】30W快充头</t>
+  </si>
+  <si>
+    <t>平果15编织线【C-C】【2米】苹果15全系列30W编织线</t>
+  </si>
+  <si>
+    <t>荣max 66W快充头+2米线</t>
+  </si>
+  <si>
+    <t>华66双口头 【66W快充头+1米线+2米线】</t>
+  </si>
+  <si>
+    <t>华66w双口头【A+C】-25w,华6a线-1米,华6a线-2米</t>
+  </si>
+  <si>
+    <t>爆款数据线一加闪充线双tpc|1.5米线(一条)</t>
+  </si>
+  <si>
+    <t>华66双口头【66W快充头+1米线+2米线】</t>
+  </si>
+  <si>
+    <t>爆款数据线一加闪充线usb|1米线(两条)</t>
+  </si>
+  <si>
+    <t>VO【44W闪充头+2米线】</t>
+  </si>
+  <si>
+    <t>爆款数据线vivo超级快充线|1.5米线(两条)</t>
+  </si>
+  <si>
+    <t>华6a线6A充电线1.5米</t>
+  </si>
+  <si>
+    <t>OPPO【65W闪充头+1.5米线】</t>
+  </si>
+  <si>
+    <t>vivo充电器USB口闪充线【1.5米】</t>
+  </si>
+  <si>
+    <t>vivo充电器【90W闪充头一个】</t>
+  </si>
+  <si>
+    <t>vivo充电器【90W闪充头+1米+1.5米线】配2线</t>
+  </si>
+  <si>
+    <t>V90W头USB-22.5w,VO120W线【USB-C】-1.5米,VO120W线【USB-C】-1米</t>
+  </si>
+  <si>
+    <t>米6a金标线黑鲨Type-c闪充线【2米】</t>
+  </si>
+  <si>
+    <t>荣耀充电器【35W快充头一个】</t>
+  </si>
+  <si>
+    <t>华6a线 6A线【1.5米线】</t>
+  </si>
+  <si>
+    <t>华100w双口头【100W快充头+1.5米线】套装</t>
+  </si>
+  <si>
+    <t>vivo充电器【90W闪充头+1.5米线】套装</t>
+  </si>
+  <si>
+    <t>VO120W线【USB-C】-1.5米,V90W头USB-22.5w</t>
+  </si>
+  <si>
+    <t>华100w双口头【100W快充头+1米线】套装</t>
+  </si>
+  <si>
+    <t>Y300GT数据线90W闪充线【1米】</t>
+  </si>
+  <si>
+    <t>vivo充电器【90W闪充头+1米线】套装</t>
+  </si>
+  <si>
+    <t>VO120W线【USB-C】-1米,V90W头USB-22.5w</t>
+  </si>
+  <si>
+    <t>荣耀数据线6A快充线【1米+1.5米】</t>
+  </si>
+  <si>
+    <t>爆款数据线苹果6-14线usb|1米线(两条)</t>
+  </si>
+  <si>
+    <t>一嘉红线【USB-C】 10A闪充线【1.5米线】</t>
+  </si>
+  <si>
+    <t>华100w双口头【100W快充头+1.5米+2米线】</t>
+  </si>
+  <si>
+    <t>华100w双口头【A+C】-25w,华6a线-1.5米,华6a线-2米</t>
+  </si>
+  <si>
+    <t>真我数据线80W闪充线【1米】</t>
+  </si>
+  <si>
+    <t>荣耀数据线6A快充线【1米】</t>
+  </si>
+  <si>
+    <t>OPPO数据线【80W闪充头+1.5米线】套装</t>
+  </si>
+  <si>
+    <t>vivo充电器双C口闪充线【1.5米】</t>
+  </si>
+  <si>
+    <t>Pura80数据线Pura80全系列6A双C快充线【1米】</t>
+  </si>
+  <si>
+    <t>荣耀充电器【35W快充头+1米线】套装</t>
+  </si>
+  <si>
+    <t>max40w大壳头G【套装】40W闪充头+1米线</t>
+  </si>
+  <si>
+    <t>Pura80数据线Pura80全系6A双C快充线【1.5米】</t>
+  </si>
+  <si>
+    <t>OPPO充电器【80W闪充头+2米线】套装</t>
+  </si>
+  <si>
+    <t>OPPO 闪充线【1.5米线】</t>
+  </si>
+  <si>
+    <t>ipad数据线iPad 11专用30W编织线【1.5米】</t>
+  </si>
+  <si>
+    <t>OPPO数据线【80W闪充头+1米线】套装</t>
+  </si>
+  <si>
+    <t>Nova14数据线6A双C快充线【2米】</t>
+  </si>
+  <si>
+    <t>iPad数据线30W编织线【1米】</t>
+  </si>
+  <si>
+    <t>OPPO数据线【80W闪充头+1米+1.5米线】配2线</t>
+  </si>
+  <si>
+    <t>OP80w头-22.5w,OP白口线【USB】-1.5米,OP白口线【USB】-1米</t>
+  </si>
+  <si>
+    <t>一加充电器竞速版【80W闪充头+1.5米线】</t>
+  </si>
+  <si>
+    <t>一嘉65W红线【C-C】1.5米线</t>
+  </si>
+  <si>
+    <t>SAM星25W黑头</t>
+  </si>
+  <si>
+    <t>一嘉65W红线【C-C】1米线</t>
+  </si>
+  <si>
+    <t>3星C-C黑色双Type-c数据线2米</t>
+  </si>
+  <si>
+    <t>苹果【iPad套装配USB口线】1米</t>
+  </si>
+  <si>
+    <t>苹果【iPad套装配USB口线】2米</t>
+  </si>
+  <si>
+    <t>平果PD线PD快充线2米</t>
+  </si>
+  <si>
+    <t>VO33W-80W线闪充数据线1.5米+2米</t>
+  </si>
+  <si>
+    <t>华6a线1.5米快充数据线+一嘉USB口红线1.5米闪充USB数据线</t>
+  </si>
+  <si>
+    <t>一嘉红线【USB-C】-1.5米,华6a线-1.5米</t>
+  </si>
+  <si>
+    <t>MI-67W金标头67W闪充头</t>
+  </si>
+  <si>
+    <t>OPr9安卓绿口线4A闪充线1.5米</t>
+  </si>
+  <si>
+    <t>max40w大壳头G【单头40W】快充头</t>
+  </si>
+  <si>
+    <t>MI-90W金标头90WD闪充头</t>
+  </si>
+  <si>
+    <t>一嘉100WD【单头】100w闪充头</t>
+  </si>
+  <si>
+    <t>一嘉65W红线【C-C】2米线</t>
+  </si>
+  <si>
+    <t>OP【150-240w看后面】高攻 150W光速秒充 【单头】</t>
+  </si>
+  <si>
+    <t>OP-65W头【套装】65W闪充头+1.5米线+65W头【2头1线】</t>
+  </si>
+  <si>
+    <t>OP65w头-22.5w,OP65w头-22.5w,OP白口线【USB】-1.5米</t>
+  </si>
+  <si>
+    <t>平果PD线PD快充线1米</t>
+  </si>
+  <si>
+    <t>OP240W线【C-C】1..5米双type-c接口12A线</t>
+  </si>
+  <si>
+    <t>一嘉USB口红线.1.5米闪充USB数据线</t>
+  </si>
+  <si>
+    <t>一加充电器Ace/Pro 150W秒充头+1米+1.5米线</t>
+  </si>
+  <si>
+    <t>一加充电器Ace/Pro  150W秒充头+1米+2米线</t>
+  </si>
+  <si>
+    <t>一加充电器Ace/Pro150W秒充头+1.5米+2米线</t>
+  </si>
+  <si>
+    <t>一加充电器Ace/Pro专用【150W秒充头一个】</t>
+  </si>
+  <si>
+    <t>一加充电器Ace/Pro【150W秒充头+1米线】</t>
+  </si>
+  <si>
+    <t>一加充电器Ace/Pro【150W秒充头+1.5米线】</t>
+  </si>
+  <si>
+    <t>一加充电器Ace/Pro【150W秒充头+2米线】</t>
+  </si>
+  <si>
+    <t>Pura80数据线Pura80全系列6A双C快充线【2米】</t>
+  </si>
+  <si>
+    <t>Pura80数据线Pura80双C快充线【1米+1.5米】</t>
+  </si>
+  <si>
+    <t>Pura80数据线Pura80双C快充线【1米+2米】</t>
+  </si>
+  <si>
+    <t>Pura80数据线Pura806A双C快充线【1.5米+2米】</t>
+  </si>
+  <si>
+    <t>Pura80数据线Pura80双C快充线 1米+1.5米+2米</t>
+  </si>
+  <si>
+    <t>一加充电器竞速版【80W闪充头+2米线】</t>
+  </si>
+  <si>
+    <t>一加充电器竞速版【80W闪充头+1米线】</t>
+  </si>
+  <si>
+    <t>一加充电器竞速版【80W闪充头一个】</t>
+  </si>
+  <si>
+    <t>一加充电器至尊版【100W闪充头+2米线】</t>
+  </si>
+  <si>
+    <t>一加充电器至尊版【100W闪充头+1.5米线】</t>
+  </si>
+  <si>
+    <t>一加充电器至尊版【100W闪充头+1米线】</t>
+  </si>
+  <si>
+    <t>一加充电器至尊版【100W闪充头一个】</t>
+  </si>
+  <si>
+    <t>Y300GT数据线90W闪充线【2米】</t>
+  </si>
+  <si>
+    <t>Y300GT数据线90W闪充线【1米+1.5米】</t>
+  </si>
+  <si>
+    <t>Y300GT数据线90W闪充线【1米+2米】</t>
+  </si>
+  <si>
+    <t>Y300GT数据线90W闪充线【1.5米+2米】</t>
+  </si>
+  <si>
+    <t>Y300GT数据线90W闪充线【1米+1.5米+2米】</t>
+  </si>
+  <si>
+    <t>Y300GT数据线90W闪充线【1.5米】</t>
+  </si>
+  <si>
+    <t>OPPO数据线【80W闪充头一个】</t>
+  </si>
+  <si>
+    <t>OPPO数据线【80W闪充头+2米线】套装</t>
+  </si>
+  <si>
+    <t>OPPO数据线【80W闪充头+1米+2米线】配2线</t>
+  </si>
+  <si>
+    <t>OPPO数据线【80W闪充头+1.5米+2米线】配2线</t>
+  </si>
+  <si>
+    <t>Nova14数据线6A双C快充线【1.5米+2米】</t>
+  </si>
+  <si>
+    <t>Nova14数据线6A双C快充线【1米+2米】</t>
+  </si>
+  <si>
+    <t>Nova14数据线6A双C快充线【1米+1.5米+2米】</t>
+  </si>
+  <si>
+    <t>Nova14数据线6A双C快充线【1.5米】</t>
+  </si>
+  <si>
+    <t>Nova14数据线6A双C快充线【1米】</t>
+  </si>
+  <si>
+    <t>Nova14数据线6A双C快充线【1米+1.5米】</t>
+  </si>
+  <si>
+    <t>荣耀充电器【35W快充头+1.5米+2米线】配2线</t>
+  </si>
+  <si>
+    <t>荣耀充电器【35W快充头+1米+2米线】配2线</t>
+  </si>
+  <si>
+    <t>荣耀充电器【35W快充头+1.5米线】套装</t>
+  </si>
+  <si>
+    <t>荣耀充电器【35W快充头+1米+1.5米线】配2线</t>
+  </si>
+  <si>
+    <t>荣耀充电器【35W快充头+2米线】套装</t>
+  </si>
+  <si>
+    <t>ipad数据线30W编织线【1米+2米】</t>
+  </si>
+  <si>
+    <t>ipad数据线30W编织线【1.5米+2米】</t>
+  </si>
+  <si>
+    <t>ipad数据线30W编织线【1米+1.5米+2米】</t>
+  </si>
+  <si>
+    <t>ipad数据线iPad 11专用30W编织线【1米】</t>
+  </si>
+  <si>
+    <t>ipad数据线iPad 11专用30W编织线【2米】</t>
+  </si>
+  <si>
+    <t>ipad数据线30W编织线【1米+1.5米】</t>
+  </si>
+  <si>
+    <t>vivo充电器【90W闪充头+1.5米+2米线】配2线</t>
+  </si>
+  <si>
+    <t>vivo充电器【90W闪充头+1米+2米线】配2线</t>
+  </si>
+  <si>
+    <t>vivo充电器【90W闪充头+2米线】套装</t>
+  </si>
+  <si>
+    <t>OPPO数据线8A闪充线【1米+1.5米+2米】</t>
+  </si>
+  <si>
+    <t>OPPO数据线8A闪充线【1.5米+2米】</t>
+  </si>
+  <si>
+    <t>OPPO数据线8A闪充线【1米+2米】</t>
+  </si>
+  <si>
+    <t>OPPO数据线8A闪充线【1米+1.5米】</t>
+  </si>
+  <si>
+    <t>OPPO数据线80W闪充线【2米】</t>
+  </si>
+  <si>
+    <t>OPPO数据线80W闪充线【1.5米】</t>
+  </si>
+  <si>
+    <t>OPPO数据线80W闪充线【1米】</t>
+  </si>
+  <si>
+    <t>华为数据线【100W快充头+1米+1.5米线】</t>
+  </si>
+  <si>
+    <t>华为数据线【100W快充头+1米+2米线】</t>
+  </si>
+  <si>
+    <t>华为数据线【100W快充头+1.5米+2米线】</t>
+  </si>
+  <si>
+    <t>华为数据线【100W快充头一个】</t>
+  </si>
+  <si>
+    <t>华为数据线【100W快充头+1米线】套装</t>
+  </si>
+  <si>
+    <t>华为数据线【100W快充头+1.5米线】套装</t>
+  </si>
+  <si>
+    <t>华为数据线【100W快充头+2米线】套装</t>
+  </si>
+  <si>
+    <t>vivo充电器USB口闪充线【1米】</t>
+  </si>
+  <si>
+    <t>vivo充电器USB口闪充线【2米】</t>
+  </si>
+  <si>
+    <t>vivo充电器USB口闪充线【1米+1.5米】</t>
+  </si>
+  <si>
+    <t>vivo充电器USB口闪充线【1米+2米】</t>
+  </si>
+  <si>
+    <t>vivo充电器USB口闪充线【1.5米+2米】</t>
+  </si>
+  <si>
+    <t>vivo充电器双C口闪充线【1米】</t>
+  </si>
+  <si>
+    <t>vivo充电器【120W】双C口闪充线【2米】</t>
+  </si>
+  <si>
+    <t>vivo充电器双C口闪充线【1米+1.5米】</t>
+  </si>
+  <si>
+    <t>vivo充电器双C口闪充线【1米+2米】</t>
+  </si>
+  <si>
+    <t>vivo充电器双C口闪充线【1.5米+2米】</t>
+  </si>
+  <si>
+    <t>荣耀数据线6A快充线【1.5米+2米】</t>
+  </si>
+  <si>
+    <t>荣耀数据线6A快充线【1米+1.5米+2米】</t>
+  </si>
+  <si>
+    <t>荣耀数据线6A快充线【1.5米】</t>
+  </si>
+  <si>
+    <t>荣耀数据线6A快充线【2米】</t>
+  </si>
+  <si>
+    <t>荣耀数据线6A快充线【1米+2米】</t>
+  </si>
+  <si>
+    <t>OPPO充电器【80W闪充头一个】</t>
+  </si>
+  <si>
+    <t>OPPO充电器【80W闪充头+1.5米线】套装</t>
+  </si>
+  <si>
+    <t>OPPO充电器【80W闪充头+1米线】套装</t>
+  </si>
+  <si>
+    <t>OPPO充电器【80W闪充头+1米+1.5米线】配2线</t>
+  </si>
+  <si>
+    <t>OPPO充电器【80W闪充头+1.5米+2米线】配2线</t>
+  </si>
+  <si>
+    <t>OPPO充电器【80W闪充头+1米+2米线】配2线</t>
+  </si>
+  <si>
+    <t>iPad数据线30W编织线【2米】</t>
+  </si>
+  <si>
+    <t>iPad数据线30W编织线【1.5米】</t>
+  </si>
+  <si>
+    <t>iPad数据线30W编织线【1米+2米】</t>
+  </si>
+  <si>
+    <t>iPad数据线30W编织线【1米+1.5米】</t>
+  </si>
+  <si>
+    <t>iPad数据线30W编织线【1米+1.5米+2米】</t>
+  </si>
+  <si>
+    <t>iPad数据线30W编织线【1.5米+2米】</t>
+  </si>
+  <si>
+    <t>vivo充电器【120W闪充头+1米+1.5米线】</t>
+  </si>
+  <si>
+    <t>vivo充电器【120W闪充头+1米+2米线】</t>
+  </si>
+  <si>
+    <t>vivo充电器【120W闪充头+1.5米线】套装</t>
+  </si>
+  <si>
+    <t>vivo充电器【120W闪充头+2米线】套装</t>
+  </si>
+  <si>
+    <t>vivo充电器【120W闪充头一个】</t>
+  </si>
+  <si>
+    <t>vivo充电器【120W闪充头+1米线】套装</t>
+  </si>
+  <si>
+    <t>vivo充电器【120W闪充头+1.5米+2米线】</t>
+  </si>
+  <si>
+    <t>真我数据线80W闪充线【1米+1.5米+2米】</t>
+  </si>
+  <si>
+    <t>真我数据线80W闪充线【1.5米+2米】</t>
+  </si>
+  <si>
+    <t>真我数据线80W闪充线【1米+2米】</t>
+  </si>
+  <si>
+    <t>真我数据线80W闪充线【1米+1.5米】</t>
+  </si>
+  <si>
+    <t>真我数据线80W闪充线【2米】</t>
+  </si>
+  <si>
+    <t>真我数据线80W闪充线【1.5米】</t>
   </si>
 </sst>
 </file>
@@ -18462,11 +19075,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D4547"/>
+  <dimension ref="A1:D4637"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.875" customWidth="1"/>
-    <col min="2" max="2" width="51.125" customWidth="1"/>
+    <col min="2" max="2" width="93.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.625" customWidth="1"/>
     <col min="4" max="4" width="13.5" customWidth="1"/>
   </cols>
@@ -82127,6 +82740,726 @@
       </c>
       <c r="D4547" t="s">
         <v>6029</v>
+      </c>
+    </row>
+    <row r="4548" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4548" t="s">
+        <v>6031</v>
+      </c>
+      <c r="B4548" t="s">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="4549" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4549" t="s">
+        <v>6032</v>
+      </c>
+      <c r="B4549" t="s">
+        <v>6033</v>
+      </c>
+    </row>
+    <row r="4550" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4550" t="s">
+        <v>6034</v>
+      </c>
+      <c r="B4550" t="s">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="4551" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4551" t="s">
+        <v>6035</v>
+      </c>
+      <c r="B4551" t="s">
+        <v>3669</v>
+      </c>
+    </row>
+    <row r="4552" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4552" t="s">
+        <v>6036</v>
+      </c>
+      <c r="B4552" t="s">
+        <v>3653</v>
+      </c>
+    </row>
+    <row r="4553" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4553" t="s">
+        <v>6037</v>
+      </c>
+      <c r="B4553" t="s">
+        <v>6038</v>
+      </c>
+    </row>
+    <row r="4554" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4554" t="s">
+        <v>6039</v>
+      </c>
+      <c r="B4554" t="s">
+        <v>4134</v>
+      </c>
+    </row>
+    <row r="4555" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4555" t="s">
+        <v>6040</v>
+      </c>
+      <c r="B4555" t="s">
+        <v>5510</v>
+      </c>
+    </row>
+    <row r="4556" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4556" t="s">
+        <v>6041</v>
+      </c>
+      <c r="B4556" t="s">
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="4557" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4557" t="s">
+        <v>6042</v>
+      </c>
+      <c r="B4557" t="s">
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="4558" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4558" t="s">
+        <v>6043</v>
+      </c>
+      <c r="B4558" t="s">
+        <v>4083</v>
+      </c>
+    </row>
+    <row r="4559" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4559" t="s">
+        <v>6044</v>
+      </c>
+      <c r="B4559" t="s">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="4560" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4560" t="s">
+        <v>6045</v>
+      </c>
+      <c r="B4560" t="s">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="4561" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4561" t="s">
+        <v>6046</v>
+      </c>
+      <c r="B4561" t="s">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="4562" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4562" t="s">
+        <v>6047</v>
+      </c>
+      <c r="B4562" t="s">
+        <v>5793</v>
+      </c>
+    </row>
+    <row r="4563" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4563" t="s">
+        <v>6048</v>
+      </c>
+      <c r="B4563" t="s">
+        <v>3429</v>
+      </c>
+    </row>
+    <row r="4564" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4564" t="s">
+        <v>6049</v>
+      </c>
+      <c r="B4564" t="s">
+        <v>3667</v>
+      </c>
+    </row>
+    <row r="4565" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4565" t="s">
+        <v>6050</v>
+      </c>
+      <c r="B4565" t="s">
+        <v>3879</v>
+      </c>
+    </row>
+    <row r="4566" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4566" t="s">
+        <v>6051</v>
+      </c>
+      <c r="B4566" t="s">
+        <v>6021</v>
+      </c>
+    </row>
+    <row r="4567" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4567" t="s">
+        <v>6052</v>
+      </c>
+      <c r="B4567" t="s">
+        <v>3565</v>
+      </c>
+    </row>
+    <row r="4568" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4568" t="s">
+        <v>6053</v>
+      </c>
+      <c r="B4568" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="4569" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4569" t="s">
+        <v>6054</v>
+      </c>
+      <c r="B4569" t="s">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="4570" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4570" t="s">
+        <v>6055</v>
+      </c>
+      <c r="B4570" t="s">
+        <v>6056</v>
+      </c>
+    </row>
+    <row r="4571" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4571" t="s">
+        <v>6057</v>
+      </c>
+      <c r="B4571" t="s">
+        <v>3699</v>
+      </c>
+    </row>
+    <row r="4572" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4572" t="s">
+        <v>6058</v>
+      </c>
+      <c r="B4572" t="s">
+        <v>3754</v>
+      </c>
+    </row>
+    <row r="4573" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4573" t="s">
+        <v>6059</v>
+      </c>
+      <c r="B4573" t="s">
+        <v>3533</v>
+      </c>
+    </row>
+    <row r="4574" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4574" t="s">
+        <v>6060</v>
+      </c>
+      <c r="B4574" t="s">
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="4575" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4575" t="s">
+        <v>6061</v>
+      </c>
+      <c r="B4575" t="s">
+        <v>3666</v>
+      </c>
+    </row>
+    <row r="4576" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4576" t="s">
+        <v>6062</v>
+      </c>
+      <c r="B4576" t="s">
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="4577" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4577" t="s">
+        <v>6063</v>
+      </c>
+      <c r="B4577" t="s">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="4578" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4578" t="s">
+        <v>6064</v>
+      </c>
+      <c r="B4578" t="s">
+        <v>3544</v>
+      </c>
+    </row>
+    <row r="4579" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4579" t="s">
+        <v>6065</v>
+      </c>
+      <c r="B4579" t="s">
+        <v>6066</v>
+      </c>
+    </row>
+    <row r="4580" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4580" t="s">
+        <v>6067</v>
+      </c>
+      <c r="B4580" t="s">
+        <v>3449</v>
+      </c>
+    </row>
+    <row r="4581" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4581" t="s">
+        <v>6068</v>
+      </c>
+      <c r="B4581" t="s">
+        <v>6066</v>
+      </c>
+    </row>
+    <row r="4582" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4582" t="s">
+        <v>6069</v>
+      </c>
+      <c r="B4582" t="s">
+        <v>5420</v>
+      </c>
+    </row>
+    <row r="4583" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4583" t="s">
+        <v>6070</v>
+      </c>
+      <c r="B4583" t="s">
+        <v>3763</v>
+      </c>
+    </row>
+    <row r="4584" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4584" t="s">
+        <v>6071</v>
+      </c>
+      <c r="B4584" t="s">
+        <v>3732</v>
+      </c>
+    </row>
+    <row r="4585" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4585" t="s">
+        <v>6072</v>
+      </c>
+      <c r="B4585" t="s">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="4586" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4586" t="s">
+        <v>6073</v>
+      </c>
+      <c r="B4586" t="s">
+        <v>4103</v>
+      </c>
+    </row>
+    <row r="4587" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4587" t="s">
+        <v>6074</v>
+      </c>
+      <c r="B4587" t="s">
+        <v>3748</v>
+      </c>
+    </row>
+    <row r="4588" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4588" t="s">
+        <v>6075</v>
+      </c>
+      <c r="B4588" t="s">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="4589" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4589" t="s">
+        <v>6076</v>
+      </c>
+      <c r="B4589" t="s">
+        <v>6077</v>
+      </c>
+    </row>
+    <row r="4590" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4590" t="s">
+        <v>6078</v>
+      </c>
+      <c r="B4590" t="s">
+        <v>3481</v>
+      </c>
+    </row>
+    <row r="4591" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4591" t="s">
+        <v>6079</v>
+      </c>
+      <c r="B4591" t="s">
+        <v>3533</v>
+      </c>
+    </row>
+    <row r="4592" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4592" t="s">
+        <v>6080</v>
+      </c>
+      <c r="B4592" t="s">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="4593" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4593" t="s">
+        <v>6081</v>
+      </c>
+      <c r="B4593" t="s">
+        <v>4045</v>
+      </c>
+    </row>
+    <row r="4594" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4594" t="s">
+        <v>6082</v>
+      </c>
+      <c r="B4594" t="s">
+        <v>6083</v>
+      </c>
+    </row>
+    <row r="4595" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4595" t="s">
+        <v>6084</v>
+      </c>
+      <c r="B4595" t="s">
+        <v>4036</v>
+      </c>
+    </row>
+    <row r="4596" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4596" t="s">
+        <v>6085</v>
+      </c>
+      <c r="B4596" t="s">
+        <v>3746</v>
+      </c>
+    </row>
+    <row r="4597" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4597" t="s">
+        <v>6086</v>
+      </c>
+      <c r="B4597" t="s">
+        <v>6087</v>
+      </c>
+    </row>
+    <row r="4598" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4598" t="s">
+        <v>6088</v>
+      </c>
+      <c r="B4598" t="s">
+        <v>5510</v>
+      </c>
+    </row>
+    <row r="4599" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4599" t="s">
+        <v>6089</v>
+      </c>
+      <c r="B4599" t="s">
+        <v>3604</v>
+      </c>
+    </row>
+    <row r="4600" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4600" t="s">
+        <v>6090</v>
+      </c>
+      <c r="B4600" t="s">
+        <v>3438</v>
+      </c>
+    </row>
+    <row r="4601" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4601" t="s">
+        <v>6091</v>
+      </c>
+      <c r="B4601" t="s">
+        <v>6092</v>
+      </c>
+    </row>
+    <row r="4602" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4602" t="s">
+        <v>6093</v>
+      </c>
+      <c r="B4602" t="s">
+        <v>3429</v>
+      </c>
+    </row>
+    <row r="4603" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4603" t="s">
+        <v>6094</v>
+      </c>
+      <c r="B4603" t="s">
+        <v>3566</v>
+      </c>
+    </row>
+    <row r="4604" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4604" t="s">
+        <v>6095</v>
+      </c>
+      <c r="B4604" t="s">
+        <v>3879</v>
+      </c>
+    </row>
+    <row r="4605" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4605" t="s">
+        <v>6096</v>
+      </c>
+      <c r="B4605" t="s">
+        <v>3738</v>
+      </c>
+    </row>
+    <row r="4606" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4606" t="s">
+        <v>6097</v>
+      </c>
+      <c r="B4606" t="s">
+        <v>3697</v>
+      </c>
+    </row>
+    <row r="4607" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4607" t="s">
+        <v>6098</v>
+      </c>
+      <c r="B4607" t="s">
+        <v>3541</v>
+      </c>
+    </row>
+    <row r="4608" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4608" t="s">
+        <v>6099</v>
+      </c>
+      <c r="B4608" t="s">
+        <v>3541</v>
+      </c>
+    </row>
+    <row r="4609" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4609" t="s">
+        <v>6100</v>
+      </c>
+      <c r="B4609" t="s">
+        <v>3699</v>
+      </c>
+    </row>
+    <row r="4610" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4610" t="s">
+        <v>6101</v>
+      </c>
+      <c r="B4610" t="s">
+        <v>3877</v>
+      </c>
+    </row>
+    <row r="4611" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4611" t="s">
+        <v>6102</v>
+      </c>
+      <c r="B4611" t="s">
+        <v>3431</v>
+      </c>
+    </row>
+    <row r="4612" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4612" t="s">
+        <v>6103</v>
+      </c>
+      <c r="B4612" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="4613" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4613" t="s">
+        <v>6104</v>
+      </c>
+      <c r="B4613" t="s">
+        <v>3878</v>
+      </c>
+    </row>
+    <row r="4614" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4614" t="s">
+        <v>6105</v>
+      </c>
+      <c r="B4614" t="s">
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="4615" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4615" t="s">
+        <v>6106</v>
+      </c>
+      <c r="B4615" t="s">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="4616" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4616" t="s">
+        <v>6107</v>
+      </c>
+      <c r="B4616" t="s">
+        <v>6108</v>
+      </c>
+    </row>
+    <row r="4617" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4617" t="s">
+        <v>6109</v>
+      </c>
+      <c r="B4617" t="s">
+        <v>3465</v>
+      </c>
+    </row>
+    <row r="4618" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4618" t="s">
+        <v>6110</v>
+      </c>
+      <c r="B4618" t="s">
+        <v>3449</v>
+      </c>
+    </row>
+    <row r="4619" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4619" t="s">
+        <v>6111</v>
+      </c>
+      <c r="B4619" t="s">
+        <v>3524</v>
+      </c>
+    </row>
+    <row r="4620" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4620" t="s">
+        <v>6112</v>
+      </c>
+      <c r="B4620" t="s">
+        <v>3448</v>
+      </c>
+    </row>
+    <row r="4621" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4621" t="s">
+        <v>6113</v>
+      </c>
+      <c r="B4621" t="s">
+        <v>3910</v>
+      </c>
+    </row>
+    <row r="4622" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4622" t="s">
+        <v>6114</v>
+      </c>
+      <c r="B4622" t="s">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="4623" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4623" t="s">
+        <v>6115</v>
+      </c>
+      <c r="B4623" t="s">
+        <v>3571</v>
+      </c>
+    </row>
+    <row r="4624" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4624" t="s">
+        <v>6116</v>
+      </c>
+      <c r="B4624" t="s">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="4625" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4625" t="s">
+        <v>6117</v>
+      </c>
+      <c r="B4625" t="s">
+        <v>3731</v>
+      </c>
+    </row>
+    <row r="4626" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4626" t="s">
+        <v>6118</v>
+      </c>
+      <c r="B4626" t="s">
+        <v>6119</v>
+      </c>
+    </row>
+    <row r="4627" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4627" t="s">
+        <v>6120</v>
+      </c>
+      <c r="B4627" t="s">
+        <v>3502</v>
+      </c>
+    </row>
+    <row r="4628" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4628" t="s">
+        <v>6121</v>
+      </c>
+      <c r="B4628" t="s">
+        <v>3806</v>
+      </c>
+    </row>
+    <row r="4629" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4629" t="s">
+        <v>6122</v>
+      </c>
+      <c r="B4629" t="s">
+        <v>3533</v>
+      </c>
+    </row>
+    <row r="4630" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4630" t="s">
+        <v>6123</v>
+      </c>
+      <c r="B4630" t="s">
+        <v>3893</v>
+      </c>
+    </row>
+    <row r="4631" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4631" t="s">
+        <v>6124</v>
+      </c>
+      <c r="B4631" t="s">
+        <v>3461</v>
+      </c>
+    </row>
+    <row r="4632" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4632" t="s">
+        <v>6125</v>
+      </c>
+      <c r="B4632" t="s">
+        <v>3447</v>
+      </c>
+    </row>
+    <row r="4633" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4633" t="s">
+        <v>6126</v>
+      </c>
+      <c r="B4633" t="s">
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="4634" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4634" t="s">
+        <v>6127</v>
+      </c>
+      <c r="B4634" t="s">
+        <v>6128</v>
+      </c>
+    </row>
+    <row r="4635" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4635" t="s">
+        <v>6129</v>
+      </c>
+      <c r="B4635" t="s">
+        <v>3578</v>
+      </c>
+    </row>
+    <row r="4636" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4636" t="s">
+        <v>6130</v>
+      </c>
+      <c r="B4636" t="s">
+        <v>3435</v>
+      </c>
+    </row>
+    <row r="4637" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4637" t="s">
+        <v>6131</v>
+      </c>
+      <c r="B4637" t="s">
+        <v>3438</v>
       </c>
     </row>
   </sheetData>
@@ -87842,4 +89175,678 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD372C9C-BC6C-4662-A82A-3A4ED6F2C47C}">
+  <dimension ref="A1:A132"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>6132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>6134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>6136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>6137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>6138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>6139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>6097</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>6140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>6141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>6142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>6143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>6144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>6109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>6145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>6146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>6147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>6148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>6149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>6150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>6151</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>6152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>6153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>6154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>6155</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>6085</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>6156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>6157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>6104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>6095</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>6158</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>6107</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>6159</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>6160</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>6161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>6162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>6163</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>6164</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>6165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>6166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>6105</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>6167</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>6168</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>6169</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>6098</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>6170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>6171</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>6079</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>6172</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>6173</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>6174</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>6175</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>6103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>6176</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>6177</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>6178</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>6076</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>6179</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>6180</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>6075</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>6086</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>6181</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>6182</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>6183</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>6184</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>6185</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>6186</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>6187</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>6188</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>6189</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>6190</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>6191</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>6192</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>6193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>6194</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>6195</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>6074</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>6196</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>6197</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>6198</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>6199</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>6096</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>6201</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>6202</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>6203</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>6204</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>6076</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>6179</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>6178</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>6075</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>6086</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>6082</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>6180</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>6205</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>6206</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>6207</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>6208</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>6088</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>6209</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>6094</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>6210</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>6211</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>6212</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>6213</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>6101</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>6214</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>6215</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>6216</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>6217</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>6218</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>6219</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>6220</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>6221</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>6106</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>6222</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>6223</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>6224</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>6225</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>6226</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>6227</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>6228</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>6229</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>6230</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>6231</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>6232</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>6233</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>6234</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>6093</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>